--- a/artfynd/A 51111-2021 artfynd.xlsx
+++ b/artfynd/A 51111-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51111-2021 artfynd.xlsx
+++ b/artfynd/A 51111-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96413824</v>
+        <v>96413782</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -721,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563062.5662148232</v>
+        <v>563053</v>
       </c>
       <c r="R2" t="n">
-        <v>6696672.381639078</v>
+        <v>6696684</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -766,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96413782</v>
+        <v>96413824</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563052.4703155161</v>
+        <v>563063</v>
       </c>
       <c r="R3" t="n">
-        <v>6696683.574282739</v>
+        <v>6696672</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96415599</v>
+        <v>96413938</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,16 +929,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -962,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563077.9432460429</v>
+        <v>563074</v>
       </c>
       <c r="R4" t="n">
-        <v>6696670.67174581</v>
+        <v>6696717</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +983,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>100-tals bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,15 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96415559</v>
+        <v>96413994</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563075.6827508357</v>
+        <v>563036</v>
       </c>
       <c r="R5" t="n">
-        <v>6696743.782581723</v>
+        <v>6696701</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1111,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1097,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>30-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,15 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96415585</v>
+        <v>96414084</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1157,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1190,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563056.3610452411</v>
+        <v>563038</v>
       </c>
       <c r="R6" t="n">
-        <v>6696687.595945207</v>
+        <v>6696718</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,27 +1235,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96414085</v>
+        <v>96415559</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,16 +1275,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1313,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563038.0118277074</v>
+        <v>563076</v>
       </c>
       <c r="R7" t="n">
-        <v>6696717.921258263</v>
+        <v>6696744</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1348,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,27 +1344,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96413938</v>
+        <v>96415585</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563073.185430904</v>
+        <v>563057</v>
       </c>
       <c r="R8" t="n">
-        <v>6696716.555198159</v>
+        <v>6696687</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1462,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,12 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>100-tals bladrosetter</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,15 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96413994</v>
+        <v>96415599</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1493,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1546,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563036.3410297091</v>
+        <v>563078</v>
       </c>
       <c r="R9" t="n">
-        <v>6696700.098990763</v>
+        <v>6696670</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1581,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,12 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>30-tal bladrosetter</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51111-2021 artfynd.xlsx
+++ b/artfynd/A 51111-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96413782</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96413824</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96413938</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96413994</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96414084</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96415559</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96415585</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1580,8 +1620,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96415599</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>